--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ideaWorkSpace\2.1.0\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>组合代码</t>
   </si>
@@ -78,6 +78,10 @@
   <si>
     <t>资产四级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -439,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="15.5" customWidth="1"/>
@@ -455,7 +459,7 @@
     <col min="14" max="14" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -506,6 +510,9 @@
       </c>
       <c r="Q1" t="s">
         <v>11</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
